--- a/data/nzd0120/nzd0120.xlsx
+++ b/data/nzd0120/nzd0120.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI252"/>
+  <dimension ref="A1:AI254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28398,6 +28398,228 @@
         <v>367.7</v>
       </c>
       <c r="AI252" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>359.61</v>
+      </c>
+      <c r="C253" t="n">
+        <v>361.16</v>
+      </c>
+      <c r="D253" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="E253" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="F253" t="n">
+        <v>351.27</v>
+      </c>
+      <c r="G253" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="H253" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="I253" t="n">
+        <v>359.74</v>
+      </c>
+      <c r="J253" t="n">
+        <v>362.53</v>
+      </c>
+      <c r="K253" t="n">
+        <v>366.31</v>
+      </c>
+      <c r="L253" t="n">
+        <v>365.44</v>
+      </c>
+      <c r="M253" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="N253" t="n">
+        <v>358.37</v>
+      </c>
+      <c r="O253" t="n">
+        <v>356.43</v>
+      </c>
+      <c r="P253" t="n">
+        <v>350.32</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>354.12</v>
+      </c>
+      <c r="R253" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="S253" t="n">
+        <v>355.55</v>
+      </c>
+      <c r="T253" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="U253" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="V253" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="W253" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="X253" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>390.41</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>387.65</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>382</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>364.76</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>376.66</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>367.22</v>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>359.61</v>
+      </c>
+      <c r="C254" t="n">
+        <v>361.16</v>
+      </c>
+      <c r="D254" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="E254" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="F254" t="n">
+        <v>351.27</v>
+      </c>
+      <c r="G254" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="H254" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="I254" t="n">
+        <v>359.74</v>
+      </c>
+      <c r="J254" t="n">
+        <v>362.53</v>
+      </c>
+      <c r="K254" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="L254" t="n">
+        <v>364.35</v>
+      </c>
+      <c r="M254" t="n">
+        <v>359.13</v>
+      </c>
+      <c r="N254" t="n">
+        <v>356.84</v>
+      </c>
+      <c r="O254" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="P254" t="n">
+        <v>349.45</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>353.52</v>
+      </c>
+      <c r="R254" t="n">
+        <v>361.84</v>
+      </c>
+      <c r="S254" t="n">
+        <v>353.04</v>
+      </c>
+      <c r="T254" t="n">
+        <v>361.97</v>
+      </c>
+      <c r="U254" t="n">
+        <v>371.51</v>
+      </c>
+      <c r="V254" t="n">
+        <v>371.41</v>
+      </c>
+      <c r="W254" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="X254" t="n">
+        <v>379.32</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>388.39</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>387.13</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>382.33</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>370.56</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>364.77</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>367.74</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>383.72</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>367.03</v>
+      </c>
+      <c r="AI254" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28414,7 +28636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30947,6 +31169,26 @@
       </c>
       <c r="B253" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -31115,28 +31357,28 @@
         <v>0.0663</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.136894200954489</v>
+        <v>-0.1404188860663766</v>
       </c>
       <c r="J2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K2" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003089648996819183</v>
+        <v>0.00330633685399262</v>
       </c>
       <c r="M2" t="n">
-        <v>14.6946070308902</v>
+        <v>14.58748205385569</v>
       </c>
       <c r="N2" t="n">
-        <v>298.0565213756427</v>
+        <v>295.6687584520353</v>
       </c>
       <c r="O2" t="n">
-        <v>17.26431352170259</v>
+        <v>17.19502132746672</v>
       </c>
       <c r="P2" t="n">
-        <v>365.3872003986892</v>
+        <v>365.4284833612209</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31193,28 +31435,28 @@
         <v>0.0613</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2913774451323519</v>
+        <v>-0.2892472691149582</v>
       </c>
       <c r="J3" t="n">
+        <v>253</v>
+      </c>
+      <c r="K3" t="n">
         <v>251</v>
       </c>
-      <c r="K3" t="n">
-        <v>249</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01414489075587988</v>
+        <v>0.01417837182047132</v>
       </c>
       <c r="M3" t="n">
-        <v>13.9039057792252</v>
+        <v>13.80562484884832</v>
       </c>
       <c r="N3" t="n">
-        <v>290.1992665853815</v>
+        <v>287.8999288506157</v>
       </c>
       <c r="O3" t="n">
-        <v>17.03523602963521</v>
+        <v>16.96761411780147</v>
       </c>
       <c r="P3" t="n">
-        <v>367.6738879685357</v>
+        <v>367.6489198380784</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31271,28 +31513,28 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3083398569718405</v>
+        <v>-0.3091740271046824</v>
       </c>
       <c r="J4" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K4" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01559222430270346</v>
+        <v>0.01594389663844897</v>
       </c>
       <c r="M4" t="n">
-        <v>14.15023131748706</v>
+        <v>14.04068631659366</v>
       </c>
       <c r="N4" t="n">
-        <v>294.5266356814726</v>
+        <v>292.1724019257104</v>
       </c>
       <c r="O4" t="n">
-        <v>17.16177833680043</v>
+        <v>17.09305127605105</v>
       </c>
       <c r="P4" t="n">
-        <v>363.6007346155364</v>
+        <v>363.6104979908096</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31349,28 +31591,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2505243400666927</v>
+        <v>-0.2478844320648665</v>
       </c>
       <c r="J5" t="n">
+        <v>253</v>
+      </c>
+      <c r="K5" t="n">
         <v>251</v>
       </c>
-      <c r="K5" t="n">
-        <v>249</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01141325510086899</v>
+        <v>0.01136848267688584</v>
       </c>
       <c r="M5" t="n">
-        <v>13.1528337491493</v>
+        <v>13.06163932944866</v>
       </c>
       <c r="N5" t="n">
-        <v>266.9073169044268</v>
+        <v>264.8003722960481</v>
       </c>
       <c r="O5" t="n">
-        <v>16.33729833553966</v>
+        <v>16.27268792474212</v>
       </c>
       <c r="P5" t="n">
-        <v>360.0821462837505</v>
+        <v>360.0512981570156</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31427,28 +31669,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2858910116548897</v>
+        <v>-0.2928069804558469</v>
       </c>
       <c r="J6" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K6" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01910613981665321</v>
+        <v>0.02034759095948602</v>
       </c>
       <c r="M6" t="n">
-        <v>11.56026824668673</v>
+        <v>11.49551962768252</v>
       </c>
       <c r="N6" t="n">
-        <v>207.7661342288362</v>
+        <v>206.2624076096285</v>
       </c>
       <c r="O6" t="n">
-        <v>14.41409498473061</v>
+        <v>14.36183858736856</v>
       </c>
       <c r="P6" t="n">
-        <v>363.1655708796711</v>
+        <v>363.2460175769708</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31505,28 +31747,28 @@
         <v>0.0993</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.330818195822592</v>
+        <v>-0.3336946833375519</v>
       </c>
       <c r="J7" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K7" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02297744534757284</v>
+        <v>0.02376009913251753</v>
       </c>
       <c r="M7" t="n">
-        <v>12.41792179099235</v>
+        <v>12.33215543094314</v>
       </c>
       <c r="N7" t="n">
-        <v>230.4126490942242</v>
+        <v>228.615198321964</v>
       </c>
       <c r="O7" t="n">
-        <v>15.17934942921548</v>
+        <v>15.1200263995128</v>
       </c>
       <c r="P7" t="n">
-        <v>366.3797500625852</v>
+        <v>366.4132093490319</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31583,28 +31825,28 @@
         <v>0.0776</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4102223700606099</v>
+        <v>-0.4093950521201429</v>
       </c>
       <c r="J8" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K8" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03565192379657633</v>
+        <v>0.03610295668001751</v>
       </c>
       <c r="M8" t="n">
-        <v>12.18618475564933</v>
+        <v>12.09328223255986</v>
       </c>
       <c r="N8" t="n">
-        <v>225.3794005466072</v>
+        <v>223.5997303745546</v>
       </c>
       <c r="O8" t="n">
-        <v>15.01264135808909</v>
+        <v>14.95325149840511</v>
       </c>
       <c r="P8" t="n">
-        <v>369.8933305072208</v>
+        <v>369.8837069636894</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31661,28 +31903,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4568277257134162</v>
+        <v>-0.4661370485575868</v>
       </c>
       <c r="J9" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K9" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04694425901634036</v>
+        <v>0.04952489068295629</v>
       </c>
       <c r="M9" t="n">
-        <v>11.82602449438315</v>
+        <v>11.78008918804319</v>
       </c>
       <c r="N9" t="n">
-        <v>209.7806435835511</v>
+        <v>208.3735953341508</v>
       </c>
       <c r="O9" t="n">
-        <v>14.48380625331446</v>
+        <v>14.43515137898286</v>
       </c>
       <c r="P9" t="n">
-        <v>377.690255787763</v>
+        <v>377.7985420040906</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31739,28 +31981,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5533809289532734</v>
+        <v>-0.5662355921244505</v>
       </c>
       <c r="J10" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K10" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06776780972417307</v>
+        <v>0.07170465653247837</v>
       </c>
       <c r="M10" t="n">
-        <v>11.71752175503099</v>
+        <v>11.69191651798805</v>
       </c>
       <c r="N10" t="n">
-        <v>208.5805045664725</v>
+        <v>207.4107967075736</v>
       </c>
       <c r="O10" t="n">
-        <v>14.44231645431135</v>
+        <v>14.40176366656437</v>
       </c>
       <c r="P10" t="n">
-        <v>385.2368951132641</v>
+        <v>385.386420822649</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31817,28 +32059,28 @@
         <v>0.0703</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7451571604672268</v>
+        <v>-0.7563433530700793</v>
       </c>
       <c r="J11" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K11" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09083314431570122</v>
+        <v>0.09466615253217436</v>
       </c>
       <c r="M11" t="n">
-        <v>12.92763603646756</v>
+        <v>12.8820069832939</v>
       </c>
       <c r="N11" t="n">
-        <v>276.2295523663249</v>
+        <v>274.4080569279408</v>
       </c>
       <c r="O11" t="n">
-        <v>16.62015500428095</v>
+        <v>16.56526658185556</v>
       </c>
       <c r="P11" t="n">
-        <v>392.1518323398493</v>
+        <v>392.2817265119451</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31895,28 +32137,28 @@
         <v>0.0771</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9062069509380556</v>
+        <v>-0.9154574146744792</v>
       </c>
       <c r="J12" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K12" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1312008164622491</v>
+        <v>0.1354160201803342</v>
       </c>
       <c r="M12" t="n">
-        <v>12.46399348221921</v>
+        <v>12.40976409993723</v>
       </c>
       <c r="N12" t="n">
-        <v>270.2792961863347</v>
+        <v>268.385018770395</v>
       </c>
       <c r="O12" t="n">
-        <v>16.44017324076406</v>
+        <v>16.38246070559594</v>
       </c>
       <c r="P12" t="n">
-        <v>394.8379156216395</v>
+        <v>394.9453275220728</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31973,28 +32215,28 @@
         <v>0.0861</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7552512116564074</v>
+        <v>-0.7702239900823872</v>
       </c>
       <c r="J13" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K13" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1060170064018606</v>
+        <v>0.1112075932809161</v>
       </c>
       <c r="M13" t="n">
-        <v>12.41872584205253</v>
+        <v>12.38189689074225</v>
       </c>
       <c r="N13" t="n">
-        <v>239.0626429170633</v>
+        <v>237.8180507124563</v>
       </c>
       <c r="O13" t="n">
-        <v>15.46165071772944</v>
+        <v>15.42135048277084</v>
       </c>
       <c r="P13" t="n">
-        <v>388.9415570545444</v>
+        <v>389.1154060214399</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32051,28 +32293,28 @@
         <v>0.1244</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8465232269572482</v>
+        <v>-0.856389724288905</v>
       </c>
       <c r="J14" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K14" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1302146027557656</v>
+        <v>0.1347037175644168</v>
       </c>
       <c r="M14" t="n">
-        <v>12.5727417587132</v>
+        <v>12.52508700608262</v>
       </c>
       <c r="N14" t="n">
-        <v>237.9059556128149</v>
+        <v>236.3050430407748</v>
       </c>
       <c r="O14" t="n">
-        <v>15.42420032328467</v>
+        <v>15.37221659490832</v>
       </c>
       <c r="P14" t="n">
-        <v>386.3263819279528</v>
+        <v>386.4409501015251</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32129,28 +32371,28 @@
         <v>0.1041</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6852758650482698</v>
+        <v>-0.6940614551784995</v>
       </c>
       <c r="J15" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K15" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1437918186111119</v>
+        <v>0.1489053907472011</v>
       </c>
       <c r="M15" t="n">
-        <v>10.01994238742383</v>
+        <v>9.978213647142679</v>
       </c>
       <c r="N15" t="n">
-        <v>138.4524871074186</v>
+        <v>137.5819595257694</v>
       </c>
       <c r="O15" t="n">
-        <v>11.76658349341127</v>
+        <v>11.72953364485432</v>
       </c>
       <c r="P15" t="n">
-        <v>380.0123282757218</v>
+        <v>380.1145250491459</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32207,28 +32449,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5944109635576993</v>
+        <v>-0.6109556932122838</v>
       </c>
       <c r="J16" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K16" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1162676274963858</v>
+        <v>0.1232243900747392</v>
       </c>
       <c r="M16" t="n">
-        <v>9.770251944028571</v>
+        <v>9.778192476543753</v>
       </c>
       <c r="N16" t="n">
-        <v>133.4783134917669</v>
+        <v>133.215897131998</v>
       </c>
       <c r="O16" t="n">
-        <v>11.55328150318198</v>
+        <v>11.54191912690424</v>
       </c>
       <c r="P16" t="n">
-        <v>375.9498160757774</v>
+        <v>376.1419168505949</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32285,28 +32527,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.567053229371691</v>
+        <v>-0.5737341229803236</v>
       </c>
       <c r="J17" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K17" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08850333769683338</v>
+        <v>0.09175977732854856</v>
       </c>
       <c r="M17" t="n">
-        <v>10.67052167852762</v>
+        <v>10.61813581433636</v>
       </c>
       <c r="N17" t="n">
-        <v>163.9712778556858</v>
+        <v>162.8050828867165</v>
       </c>
       <c r="O17" t="n">
-        <v>12.80512701443003</v>
+        <v>12.75950950807736</v>
       </c>
       <c r="P17" t="n">
-        <v>373.1066672568013</v>
+        <v>373.1843844181449</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32363,28 +32605,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5343892098122099</v>
+        <v>-0.5225476617145324</v>
       </c>
       <c r="J18" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K18" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07308829639692194</v>
+        <v>0.07108071055233756</v>
       </c>
       <c r="M18" t="n">
-        <v>11.12474264392873</v>
+        <v>11.0900882180382</v>
       </c>
       <c r="N18" t="n">
-        <v>179.3207634971903</v>
+        <v>178.3102285825376</v>
       </c>
       <c r="O18" t="n">
-        <v>13.39107028945746</v>
+        <v>13.35328531045966</v>
       </c>
       <c r="P18" t="n">
-        <v>369.1221359655529</v>
+        <v>368.9843982887663</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32441,28 +32683,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5523184506085269</v>
+        <v>-0.5541818886524171</v>
       </c>
       <c r="J19" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K19" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09670254808480117</v>
+        <v>0.09878938910777135</v>
       </c>
       <c r="M19" t="n">
-        <v>10.38410090022192</v>
+        <v>10.31224037887345</v>
       </c>
       <c r="N19" t="n">
-        <v>141.0901391843215</v>
+        <v>139.9970460089093</v>
       </c>
       <c r="O19" t="n">
-        <v>11.87813702498509</v>
+        <v>11.83203473663382</v>
       </c>
       <c r="P19" t="n">
-        <v>370.2282116254141</v>
+        <v>370.2499080930031</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32519,28 +32761,28 @@
         <v>0.0849</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3331293450198143</v>
+        <v>-0.3302472777516331</v>
       </c>
       <c r="J20" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K20" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03619629032731231</v>
+        <v>0.0361801989942282</v>
       </c>
       <c r="M20" t="n">
-        <v>10.21870076507862</v>
+        <v>10.15111486653764</v>
       </c>
       <c r="N20" t="n">
-        <v>146.8674137320405</v>
+        <v>145.7297515639</v>
       </c>
       <c r="O20" t="n">
-        <v>12.11888665398107</v>
+        <v>12.07185783398314</v>
       </c>
       <c r="P20" t="n">
-        <v>369.8196709202037</v>
+        <v>369.7862201056263</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32597,28 +32839,28 @@
         <v>0.1177</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4832400672396913</v>
+        <v>-0.4694002085812553</v>
       </c>
       <c r="J21" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K21" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05741154097351886</v>
+        <v>0.05507617910454465</v>
       </c>
       <c r="M21" t="n">
-        <v>11.59912098841335</v>
+        <v>11.57404540369391</v>
       </c>
       <c r="N21" t="n">
-        <v>189.8337723390457</v>
+        <v>188.8938284656063</v>
       </c>
       <c r="O21" t="n">
-        <v>13.77801772168427</v>
+        <v>13.74386512104969</v>
       </c>
       <c r="P21" t="n">
-        <v>376.7768564171117</v>
+        <v>376.61588414965</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32675,28 +32917,28 @@
         <v>0.07729999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6422830659736524</v>
+        <v>-0.6294466704827435</v>
       </c>
       <c r="J22" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K22" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09821187219397209</v>
+        <v>0.09595037486242297</v>
       </c>
       <c r="M22" t="n">
-        <v>11.63705703345728</v>
+        <v>11.60477837273894</v>
       </c>
       <c r="N22" t="n">
-        <v>185.1526234586688</v>
+        <v>184.162785306808</v>
       </c>
       <c r="O22" t="n">
-        <v>13.60707990197268</v>
+        <v>13.57065898572387</v>
       </c>
       <c r="P22" t="n">
-        <v>381.9767309378328</v>
+        <v>381.8262524313505</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32753,28 +32995,28 @@
         <v>0.0822</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7745000837641023</v>
+        <v>-0.7523264498209223</v>
       </c>
       <c r="J23" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K23" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1228455200329656</v>
+        <v>0.1177871852971982</v>
       </c>
       <c r="M23" t="n">
-        <v>12.23557950239639</v>
+        <v>12.23910576731333</v>
       </c>
       <c r="N23" t="n">
-        <v>212.07251782513</v>
+        <v>211.8293814990151</v>
       </c>
       <c r="O23" t="n">
-        <v>14.56270983797761</v>
+        <v>14.55435953585781</v>
       </c>
       <c r="P23" t="n">
-        <v>382.3663557295415</v>
+        <v>382.1084472617301</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32831,28 +33073,28 @@
         <v>0.1105</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7352339852328621</v>
+        <v>-0.7153727570244798</v>
       </c>
       <c r="J24" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K24" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1257549701623515</v>
+        <v>0.1210054275886938</v>
       </c>
       <c r="M24" t="n">
-        <v>11.36136152753396</v>
+        <v>11.3520673426646</v>
       </c>
       <c r="N24" t="n">
-        <v>186.0732110496865</v>
+        <v>185.7566438268489</v>
       </c>
       <c r="O24" t="n">
-        <v>13.64086548022839</v>
+        <v>13.62925690662733</v>
       </c>
       <c r="P24" t="n">
-        <v>387.97639660185</v>
+        <v>387.7453890434709</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -32909,28 +33151,28 @@
         <v>0.0989</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7127683614311594</v>
+        <v>-0.6930624438815445</v>
       </c>
       <c r="J25" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K25" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1432407359781225</v>
+        <v>0.1376215397948711</v>
       </c>
       <c r="M25" t="n">
-        <v>10.06878205539754</v>
+        <v>10.06473300558072</v>
       </c>
       <c r="N25" t="n">
-        <v>150.4574804163364</v>
+        <v>150.4022861570734</v>
       </c>
       <c r="O25" t="n">
-        <v>12.26611105511182</v>
+        <v>12.26386098082791</v>
       </c>
       <c r="P25" t="n">
-        <v>396.4041928721016</v>
+        <v>396.174989593458</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -32987,28 +33229,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5822244312978293</v>
+        <v>-0.5682852143744465</v>
       </c>
       <c r="J26" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K26" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1176915599405629</v>
+        <v>0.1140310916141631</v>
       </c>
       <c r="M26" t="n">
-        <v>9.484320467682799</v>
+        <v>9.468686317793809</v>
       </c>
       <c r="N26" t="n">
-        <v>123.9823648446974</v>
+        <v>123.550221872448</v>
       </c>
       <c r="O26" t="n">
-        <v>11.1347368556557</v>
+        <v>11.11531474464165</v>
       </c>
       <c r="P26" t="n">
-        <v>394.5468401645192</v>
+        <v>394.3832665012108</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -33065,28 +33307,28 @@
         <v>0.0572</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5493914878128258</v>
+        <v>-0.5398717854935321</v>
       </c>
       <c r="J27" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K27" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1005054202404304</v>
+        <v>0.09873661821095769</v>
       </c>
       <c r="M27" t="n">
-        <v>9.763807616663643</v>
+        <v>9.73086284489696</v>
       </c>
       <c r="N27" t="n">
-        <v>131.7883043205757</v>
+        <v>130.9997168288512</v>
       </c>
       <c r="O27" t="n">
-        <v>11.47990872440089</v>
+        <v>11.44551077186384</v>
       </c>
       <c r="P27" t="n">
-        <v>391.1208859870924</v>
+        <v>391.0091685057957</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -33143,28 +33385,28 @@
         <v>0.0688</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5360890544806355</v>
+        <v>-0.5313997955140818</v>
       </c>
       <c r="J28" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K28" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L28" t="n">
-        <v>0.09592729174198944</v>
+        <v>0.09585416133363422</v>
       </c>
       <c r="M28" t="n">
-        <v>10.04924923091063</v>
+        <v>9.991984979238657</v>
       </c>
       <c r="N28" t="n">
-        <v>132.1414313516236</v>
+        <v>131.1553161603572</v>
       </c>
       <c r="O28" t="n">
-        <v>11.49527865480535</v>
+        <v>11.4523061503069</v>
       </c>
       <c r="P28" t="n">
-        <v>382.2558668664977</v>
+        <v>382.2008408657356</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -33221,28 +33463,28 @@
         <v>0.0863</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7318758482641829</v>
+        <v>-0.7227717931221691</v>
       </c>
       <c r="J29" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K29" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1954874472992669</v>
+        <v>0.1939146502997277</v>
       </c>
       <c r="M29" t="n">
-        <v>8.735914001629324</v>
+        <v>8.710777862938658</v>
       </c>
       <c r="N29" t="n">
-        <v>107.5456209453288</v>
+        <v>106.9272541151356</v>
       </c>
       <c r="O29" t="n">
-        <v>10.37042048064247</v>
+        <v>10.34056352986314</v>
       </c>
       <c r="P29" t="n">
-        <v>378.855813707196</v>
+        <v>378.7489765187423</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -33299,28 +33541,28 @@
         <v>0.0877</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7271875431661592</v>
+        <v>-0.7124978760961688</v>
       </c>
       <c r="J30" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K30" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L30" t="n">
-        <v>0.210881729395049</v>
+        <v>0.2059356344826483</v>
       </c>
       <c r="M30" t="n">
-        <v>8.383159178008572</v>
+        <v>8.387248352608413</v>
       </c>
       <c r="N30" t="n">
-        <v>96.53836885115487</v>
+        <v>96.38444917337821</v>
       </c>
       <c r="O30" t="n">
-        <v>9.825394081213988</v>
+        <v>9.817558208300994</v>
       </c>
       <c r="P30" t="n">
-        <v>380.9724845352633</v>
+        <v>380.8000996803903</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -33377,28 +33619,28 @@
         <v>0.1087</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6486936515366237</v>
+        <v>-0.6392502718396534</v>
       </c>
       <c r="J31" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K31" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1810083199731721</v>
+        <v>0.1788146705588411</v>
       </c>
       <c r="M31" t="n">
-        <v>8.267713817234307</v>
+        <v>8.247129181072172</v>
       </c>
       <c r="N31" t="n">
-        <v>92.8889809728291</v>
+        <v>92.40500494471453</v>
       </c>
       <c r="O31" t="n">
-        <v>9.637892973717289</v>
+        <v>9.61275220447893</v>
       </c>
       <c r="P31" t="n">
-        <v>379.5611759060732</v>
+        <v>379.4503596705796</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -33455,28 +33697,28 @@
         <v>0.1004</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4200031868902875</v>
+        <v>-0.4192478287889204</v>
       </c>
       <c r="J32" t="n">
+        <v>253</v>
+      </c>
+      <c r="K32" t="n">
         <v>251</v>
       </c>
-      <c r="K32" t="n">
-        <v>249</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.08397290478696695</v>
+        <v>0.08502846583968948</v>
       </c>
       <c r="M32" t="n">
-        <v>8.232017544979538</v>
+        <v>8.169196166253649</v>
       </c>
       <c r="N32" t="n">
-        <v>92.97309369151223</v>
+        <v>92.23438479871741</v>
       </c>
       <c r="O32" t="n">
-        <v>9.642255632968473</v>
+        <v>9.603873426837602</v>
       </c>
       <c r="P32" t="n">
-        <v>387.1991979483561</v>
+        <v>387.1902823186678</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -33533,28 +33775,28 @@
         <v>0.1039</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3710167558507868</v>
+        <v>-0.3747238633235545</v>
       </c>
       <c r="J33" t="n">
+        <v>253</v>
+      </c>
+      <c r="K33" t="n">
         <v>251</v>
       </c>
-      <c r="K33" t="n">
-        <v>249</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.0803250206900642</v>
+        <v>0.08307288271596414</v>
       </c>
       <c r="M33" t="n">
-        <v>7.169429534337747</v>
+        <v>7.129936349687314</v>
       </c>
       <c r="N33" t="n">
-        <v>76.14713012225359</v>
+        <v>75.57988187385568</v>
       </c>
       <c r="O33" t="n">
-        <v>8.726232298206002</v>
+        <v>8.693669068572582</v>
       </c>
       <c r="P33" t="n">
-        <v>396.2598423717052</v>
+        <v>396.3036255447708</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -33611,28 +33853,28 @@
         <v>0.0945</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5320928678909945</v>
+        <v>-0.5369924279410631</v>
       </c>
       <c r="J34" t="n">
+        <v>253</v>
+      </c>
+      <c r="K34" t="n">
         <v>251</v>
       </c>
-      <c r="K34" t="n">
-        <v>249</v>
-      </c>
       <c r="L34" t="n">
-        <v>0.1590108579748654</v>
+        <v>0.1637012125973152</v>
       </c>
       <c r="M34" t="n">
-        <v>7.017152803193668</v>
+        <v>6.981502451074172</v>
       </c>
       <c r="N34" t="n">
-        <v>72.34715389204142</v>
+        <v>71.83793926624959</v>
       </c>
       <c r="O34" t="n">
-        <v>8.505713014911885</v>
+        <v>8.475726474246889</v>
       </c>
       <c r="P34" t="n">
-        <v>384.315440357605</v>
+        <v>384.3733003212124</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -33670,7 +33912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI252"/>
+  <dimension ref="A1:AI254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78145,6 +78387,360 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>-36.233526323747036,175.4772809044635</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>-36.23425068214008,175.4772981569452</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>-36.234976212182026,175.47722789413606</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-36.235700769774205,175.4772293556835</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-36.2364281811497,175.4771880667648</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-36.237151792775464,175.47728275808572</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-36.237870003676335,175.4774145417539</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-36.238590441292914,175.47750959886255</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-36.23930825435377,175.47763182538583</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>-36.24002364570978,175.4777645014148</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>-36.240736025910884,175.47790100784252</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>-36.241453115743354,175.4780412742281</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>-36.242162790289115,175.47822449842474</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>-36.24287325420277,175.47840372584207</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>-36.24359267966855,175.4785379109879</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>-36.244290786617704,175.47877913797225</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>-36.244979467402025,175.4790676766383</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>-36.245700250328106,175.4791949475827</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>-36.24638971381854,175.47947949121667</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>-36.24707029299213,175.4797833422487</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>-36.24774074962867,175.4800618089663</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>-36.248374187982826,175.4804774552251</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>-36.248999607820046,175.48092463171608</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>-36.24957924121007,175.48141889628914</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>-36.25016248739442,175.48191344362868</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>-36.250776721954445,175.4823959753996</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>-36.25142063478506,175.4828303502917</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>-36.2520372120093,175.48330803035614</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>-36.25256814040472,175.48390421690226</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>-36.25306993358721,175.48454177334213</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>-36.253497179481165,175.48525730919974</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>-36.25381897838393,175.4859661194334</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>-36.25411493424517,175.486756535989</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>-36.233526323747036,175.4772809044635</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>-36.23425068214008,175.4772981569452</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>-36.234976212182026,175.47722789413606</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-36.235700769774205,175.4772293556835</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-36.2364281811497,175.4771880667648</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-36.237151792775464,175.47728275808572</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-36.237870003676335,175.4774145417539</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-36.238590441292914,175.47750959886255</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-36.23930825435377,175.47763182538583</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-36.2400262662343,175.4777430553283</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>-36.24073808353035,175.47788915338438</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>-36.241454857676956,175.47803252530613</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>-36.24216608062719,175.47820797254093</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>-36.24287394238221,175.47840026941844</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>-36.24359455066356,175.4785285137527</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>-36.244292076969906,175.47877265706686</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>-36.244980456682256,175.47906270790443</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>-36.24570564837437,175.47916783533532</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>-36.2463927032058,175.47946447674448</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>-36.247074424648446,175.4797660593391</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>-36.24774887208989,175.48003827203252</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>-36.248382132591765,175.48045823325992</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>-36.249009312736796,175.48090215226267</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>-36.24958920227643,175.481400090402</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>-36.25016532465587,175.4819088404899</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>-36.25077492137723,175.48239889663685</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>-36.251422544494766,175.48282725199164</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>-36.25203715632247,175.48330811780653</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>-36.25256801595712,175.48390437780893</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>-36.253072152397216,175.48453932965825</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>-36.25350087230782,175.48525374914075</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>-36.253825216347906,175.48596291125924</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>-36.25411661237672,175.48675611822878</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0120/nzd0120.xlsx
+++ b/data/nzd0120/nzd0120.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI254"/>
+  <dimension ref="A1:AI255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28622,6 +28622,117 @@
       <c r="AI254" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="C255" t="n">
+        <v>362.07</v>
+      </c>
+      <c r="D255" t="n">
+        <v>357.22</v>
+      </c>
+      <c r="E255" t="n">
+        <v>355.37</v>
+      </c>
+      <c r="F255" t="n">
+        <v>351.34</v>
+      </c>
+      <c r="G255" t="n">
+        <v>355.23</v>
+      </c>
+      <c r="H255" t="n">
+        <v>361.34</v>
+      </c>
+      <c r="I255" t="n">
+        <v>361.67</v>
+      </c>
+      <c r="J255" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="K255" t="n">
+        <v>365.58</v>
+      </c>
+      <c r="L255" t="n">
+        <v>364.22</v>
+      </c>
+      <c r="M255" t="n">
+        <v>359.86</v>
+      </c>
+      <c r="N255" t="n">
+        <v>356.48</v>
+      </c>
+      <c r="O255" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="P255" t="n">
+        <v>349.82</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>353.56</v>
+      </c>
+      <c r="R255" t="n">
+        <v>362.12</v>
+      </c>
+      <c r="S255" t="n">
+        <v>354.69</v>
+      </c>
+      <c r="T255" t="n">
+        <v>361.8</v>
+      </c>
+      <c r="U255" t="n">
+        <v>370.96</v>
+      </c>
+      <c r="V255" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="W255" t="n">
+        <v>374.14</v>
+      </c>
+      <c r="X255" t="n">
+        <v>380.33</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>389.22</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>388</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>384.17</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>372.56</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>366.02</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>371.99</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>369.25</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>378.06</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>385.04</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>368.26</v>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28636,7 +28747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B255"/>
+  <dimension ref="A1:B256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31189,6 +31300,16 @@
       </c>
       <c r="B255" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -31357,28 +31478,28 @@
         <v>0.0663</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1404188860663766</v>
+        <v>-0.1418293499871855</v>
       </c>
       <c r="J2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00330633685399262</v>
+        <v>0.003401417325195721</v>
       </c>
       <c r="M2" t="n">
-        <v>14.58748205385569</v>
+        <v>14.53331540597689</v>
       </c>
       <c r="N2" t="n">
-        <v>295.6687584520353</v>
+        <v>294.4833675434112</v>
       </c>
       <c r="O2" t="n">
-        <v>17.19502132746672</v>
+        <v>17.16051769450477</v>
       </c>
       <c r="P2" t="n">
-        <v>365.4284833612209</v>
+        <v>365.4450329161593</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31435,28 +31556,28 @@
         <v>0.0613</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2892472691149582</v>
+        <v>-0.287467265709716</v>
       </c>
       <c r="J3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01417837182047132</v>
+        <v>0.0141227234837582</v>
       </c>
       <c r="M3" t="n">
-        <v>13.80562484884832</v>
+        <v>13.76121306886855</v>
       </c>
       <c r="N3" t="n">
-        <v>287.8999288506157</v>
+        <v>286.7760927131852</v>
       </c>
       <c r="O3" t="n">
-        <v>16.96761411780147</v>
+        <v>16.93446464206014</v>
       </c>
       <c r="P3" t="n">
-        <v>367.6489198380784</v>
+        <v>367.6280194843645</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31513,28 +31634,28 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3091740271046824</v>
+        <v>-0.3076095133457719</v>
       </c>
       <c r="J4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K4" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01594389663844897</v>
+        <v>0.01591719427933569</v>
       </c>
       <c r="M4" t="n">
-        <v>14.04068631659366</v>
+        <v>13.99293851166215</v>
       </c>
       <c r="N4" t="n">
-        <v>292.1724019257104</v>
+        <v>291.0226463095446</v>
       </c>
       <c r="O4" t="n">
-        <v>17.09305127605105</v>
+        <v>17.05938587140653</v>
       </c>
       <c r="P4" t="n">
-        <v>363.6104979908096</v>
+        <v>363.5921540865126</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31591,28 +31712,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2478844320648665</v>
+        <v>-0.2462667525018676</v>
       </c>
       <c r="J5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K5" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01136848267688584</v>
+        <v>0.01131634042289342</v>
       </c>
       <c r="M5" t="n">
-        <v>13.06163932944866</v>
+        <v>13.01808064795532</v>
       </c>
       <c r="N5" t="n">
-        <v>264.8003722960481</v>
+        <v>263.7648330460019</v>
       </c>
       <c r="O5" t="n">
-        <v>16.27268792474212</v>
+        <v>16.24083843420659</v>
       </c>
       <c r="P5" t="n">
-        <v>360.0512981570156</v>
+        <v>360.032362064669</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31669,28 +31790,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2928069804558469</v>
+        <v>-0.2960820635862356</v>
       </c>
       <c r="J6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K6" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02034759095948602</v>
+        <v>0.02096129748550801</v>
       </c>
       <c r="M6" t="n">
-        <v>11.49551962768252</v>
+        <v>11.46276248177556</v>
       </c>
       <c r="N6" t="n">
-        <v>206.2624076096285</v>
+        <v>205.5141265283101</v>
       </c>
       <c r="O6" t="n">
-        <v>14.36183858736856</v>
+        <v>14.33576389762018</v>
       </c>
       <c r="P6" t="n">
-        <v>363.2460175769708</v>
+        <v>363.2841806585791</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31747,28 +31868,28 @@
         <v>0.0993</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3336946833375519</v>
+        <v>-0.3354993613560669</v>
       </c>
       <c r="J7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02376009913251753</v>
+        <v>0.02420738468893502</v>
       </c>
       <c r="M7" t="n">
-        <v>12.33215543094314</v>
+        <v>12.29131551411465</v>
       </c>
       <c r="N7" t="n">
-        <v>228.615198321964</v>
+        <v>227.7345031353932</v>
       </c>
       <c r="O7" t="n">
-        <v>15.1200263995128</v>
+        <v>15.09087483002205</v>
       </c>
       <c r="P7" t="n">
-        <v>366.4132093490319</v>
+        <v>366.4342384563112</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31825,28 +31946,28 @@
         <v>0.0776</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4093950521201429</v>
+        <v>-0.4074238771772151</v>
       </c>
       <c r="J8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03610295668001751</v>
+        <v>0.03605598960068424</v>
       </c>
       <c r="M8" t="n">
-        <v>12.09328223255986</v>
+        <v>12.05377702529386</v>
       </c>
       <c r="N8" t="n">
-        <v>223.5997303745546</v>
+        <v>222.7425190574113</v>
       </c>
       <c r="O8" t="n">
-        <v>14.95325149840511</v>
+        <v>14.92456093348851</v>
       </c>
       <c r="P8" t="n">
-        <v>369.8837069636894</v>
+        <v>369.8607377420799</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31903,28 +32024,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4661370485575868</v>
+        <v>-0.4690632376910308</v>
       </c>
       <c r="J9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04952489068295629</v>
+        <v>0.05050730528656822</v>
       </c>
       <c r="M9" t="n">
-        <v>11.78008918804319</v>
+        <v>11.74853814650247</v>
       </c>
       <c r="N9" t="n">
-        <v>208.3735953341508</v>
+        <v>207.6041382399914</v>
       </c>
       <c r="O9" t="n">
-        <v>14.43515137898286</v>
+        <v>14.40847452855407</v>
       </c>
       <c r="P9" t="n">
-        <v>377.7985420040906</v>
+        <v>377.8326395797109</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31981,28 +32102,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5662355921244505</v>
+        <v>-0.5727798214452455</v>
       </c>
       <c r="J10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07170465653247837</v>
+        <v>0.07373808900235668</v>
       </c>
       <c r="M10" t="n">
-        <v>11.69191651798805</v>
+        <v>11.67980249904908</v>
       </c>
       <c r="N10" t="n">
-        <v>207.4107967075736</v>
+        <v>206.8488591038195</v>
       </c>
       <c r="O10" t="n">
-        <v>14.40176366656437</v>
+        <v>14.38224110157452</v>
       </c>
       <c r="P10" t="n">
-        <v>385.386420822649</v>
+        <v>385.4626778053546</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32059,28 +32180,28 @@
         <v>0.0703</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7563433530700793</v>
+        <v>-0.7615295058747209</v>
       </c>
       <c r="J11" t="n">
+        <v>254</v>
+      </c>
+      <c r="K11" t="n">
         <v>253</v>
       </c>
-      <c r="K11" t="n">
-        <v>252</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.09466615253217436</v>
+        <v>0.09652469800352159</v>
       </c>
       <c r="M11" t="n">
-        <v>12.8820069832939</v>
+        <v>12.85758488891431</v>
       </c>
       <c r="N11" t="n">
-        <v>274.4080569279408</v>
+        <v>273.4837621265236</v>
       </c>
       <c r="O11" t="n">
-        <v>16.56526658185556</v>
+        <v>16.53734447021418</v>
       </c>
       <c r="P11" t="n">
-        <v>392.2817265119451</v>
+        <v>392.3420473612261</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32137,28 +32258,28 @@
         <v>0.0771</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9154574146744792</v>
+        <v>-0.920443026431026</v>
       </c>
       <c r="J12" t="n">
+        <v>254</v>
+      </c>
+      <c r="K12" t="n">
         <v>253</v>
       </c>
-      <c r="K12" t="n">
-        <v>252</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1354160201803342</v>
+        <v>0.1376233503796517</v>
       </c>
       <c r="M12" t="n">
-        <v>12.40976409993723</v>
+        <v>12.38481697161805</v>
       </c>
       <c r="N12" t="n">
-        <v>268.385018770395</v>
+        <v>267.4723713237457</v>
       </c>
       <c r="O12" t="n">
-        <v>16.38246070559594</v>
+        <v>16.35458257870698</v>
       </c>
       <c r="P12" t="n">
-        <v>394.9453275220728</v>
+        <v>395.0033158511229</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32215,28 +32336,28 @@
         <v>0.0861</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7702239900823872</v>
+        <v>-0.7771780896755182</v>
       </c>
       <c r="J13" t="n">
+        <v>254</v>
+      </c>
+      <c r="K13" t="n">
         <v>253</v>
       </c>
-      <c r="K13" t="n">
-        <v>252</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1112075932809161</v>
+        <v>0.1137205627897069</v>
       </c>
       <c r="M13" t="n">
-        <v>12.38189689074225</v>
+        <v>12.36144751980176</v>
       </c>
       <c r="N13" t="n">
-        <v>237.8180507124563</v>
+        <v>237.1663184176259</v>
       </c>
       <c r="O13" t="n">
-        <v>15.42135048277084</v>
+        <v>15.40020514206307</v>
       </c>
       <c r="P13" t="n">
-        <v>389.1154060214399</v>
+        <v>389.1962901004949</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32293,28 +32414,28 @@
         <v>0.1244</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.856389724288905</v>
+        <v>-0.8620393242361816</v>
       </c>
       <c r="J14" t="n">
+        <v>254</v>
+      </c>
+      <c r="K14" t="n">
         <v>253</v>
       </c>
-      <c r="K14" t="n">
-        <v>252</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1347037175644168</v>
+        <v>0.1371418177175455</v>
       </c>
       <c r="M14" t="n">
-        <v>12.52508700608262</v>
+        <v>12.50519737149972</v>
       </c>
       <c r="N14" t="n">
-        <v>236.3050430407748</v>
+        <v>235.5612868382823</v>
       </c>
       <c r="O14" t="n">
-        <v>15.37221659490832</v>
+        <v>15.3480059564193</v>
       </c>
       <c r="P14" t="n">
-        <v>386.4409501015251</v>
+        <v>386.5066613676128</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32371,28 +32492,28 @@
         <v>0.1041</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6940614551784995</v>
+        <v>-0.6983260709732733</v>
       </c>
       <c r="J15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K15" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1489053907472011</v>
+        <v>0.1514410049452606</v>
       </c>
       <c r="M15" t="n">
-        <v>9.978213647142679</v>
+        <v>9.956975605723835</v>
       </c>
       <c r="N15" t="n">
-        <v>137.5819595257694</v>
+        <v>137.1484341934461</v>
       </c>
       <c r="O15" t="n">
-        <v>11.72953364485432</v>
+        <v>11.71103898864</v>
       </c>
       <c r="P15" t="n">
-        <v>380.1145250491459</v>
+        <v>380.1642187131309</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32449,28 +32570,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6109556932122838</v>
+        <v>-0.6189905872885523</v>
       </c>
       <c r="J16" t="n">
+        <v>254</v>
+      </c>
+      <c r="K16" t="n">
         <v>253</v>
       </c>
-      <c r="K16" t="n">
-        <v>252</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1232243900747392</v>
+        <v>0.1266850682549046</v>
       </c>
       <c r="M16" t="n">
-        <v>9.778192476543753</v>
+        <v>9.780728536596332</v>
       </c>
       <c r="N16" t="n">
-        <v>133.215897131998</v>
+        <v>133.0741767334918</v>
       </c>
       <c r="O16" t="n">
-        <v>11.54191912690424</v>
+        <v>11.53577811564923</v>
       </c>
       <c r="P16" t="n">
-        <v>376.1419168505949</v>
+        <v>376.2353717974158</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32527,28 +32648,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5737341229803236</v>
+        <v>-0.5771562534805412</v>
       </c>
       <c r="J17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K17" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09175977732854856</v>
+        <v>0.09342929478996975</v>
       </c>
       <c r="M17" t="n">
-        <v>10.61813581433636</v>
+        <v>10.59257216778052</v>
       </c>
       <c r="N17" t="n">
-        <v>162.8050828867165</v>
+        <v>162.2337491027664</v>
       </c>
       <c r="O17" t="n">
-        <v>12.75950950807736</v>
+        <v>12.73710128336767</v>
       </c>
       <c r="P17" t="n">
-        <v>373.1843844181449</v>
+        <v>373.2242609771069</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32605,28 +32726,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5225476617145324</v>
+        <v>-0.5167631484480715</v>
       </c>
       <c r="J18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K18" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07108071055233756</v>
+        <v>0.07009817104505556</v>
       </c>
       <c r="M18" t="n">
-        <v>11.0900882180382</v>
+        <v>11.07265474460265</v>
       </c>
       <c r="N18" t="n">
-        <v>178.3102285825376</v>
+        <v>177.8071697533706</v>
       </c>
       <c r="O18" t="n">
-        <v>13.35328531045966</v>
+        <v>13.33443548686522</v>
       </c>
       <c r="P18" t="n">
-        <v>368.9843982887663</v>
+        <v>368.9169939380784</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32683,28 +32804,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5541818886524171</v>
+        <v>-0.5547368651332248</v>
       </c>
       <c r="J19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K19" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09878938910777135</v>
+        <v>0.09971871655718589</v>
       </c>
       <c r="M19" t="n">
-        <v>10.31224037887345</v>
+        <v>10.27442782782827</v>
       </c>
       <c r="N19" t="n">
-        <v>139.9970460089093</v>
+        <v>139.447707835767</v>
       </c>
       <c r="O19" t="n">
-        <v>11.83203473663382</v>
+        <v>11.80879789969186</v>
       </c>
       <c r="P19" t="n">
-        <v>370.2499080930031</v>
+        <v>370.2563749861734</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32761,28 +32882,28 @@
         <v>0.0849</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3302472777516331</v>
+        <v>-0.3295421564244401</v>
       </c>
       <c r="J20" t="n">
+        <v>254</v>
+      </c>
+      <c r="K20" t="n">
         <v>253</v>
       </c>
-      <c r="K20" t="n">
-        <v>252</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.0361801989942282</v>
+        <v>0.03632419873842485</v>
       </c>
       <c r="M20" t="n">
-        <v>10.15111486653764</v>
+        <v>10.11426765506725</v>
       </c>
       <c r="N20" t="n">
-        <v>145.7297515639</v>
+        <v>145.1567083136429</v>
       </c>
       <c r="O20" t="n">
-        <v>12.07185783398314</v>
+        <v>12.04809978019949</v>
       </c>
       <c r="P20" t="n">
-        <v>369.7862201056263</v>
+        <v>369.7780187434789</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32839,28 +32960,28 @@
         <v>0.1177</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4694002085812553</v>
+        <v>-0.4637906778213911</v>
       </c>
       <c r="J21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K21" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05507617910454465</v>
+        <v>0.05421695450571695</v>
       </c>
       <c r="M21" t="n">
-        <v>11.57404540369391</v>
+        <v>11.55535484654023</v>
       </c>
       <c r="N21" t="n">
-        <v>188.8938284656063</v>
+        <v>188.3372474349476</v>
       </c>
       <c r="O21" t="n">
-        <v>13.74386512104969</v>
+        <v>13.72360183898336</v>
       </c>
       <c r="P21" t="n">
-        <v>376.61588414965</v>
+        <v>376.5505187919934</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32917,28 +33038,28 @@
         <v>0.07729999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6294466704827435</v>
+        <v>-0.6239738092754937</v>
       </c>
       <c r="J22" t="n">
+        <v>254</v>
+      </c>
+      <c r="K22" t="n">
         <v>253</v>
       </c>
-      <c r="K22" t="n">
-        <v>252</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.09595037486242297</v>
+        <v>0.09508946235666904</v>
       </c>
       <c r="M22" t="n">
-        <v>11.60477837273894</v>
+        <v>11.58451307581631</v>
       </c>
       <c r="N22" t="n">
-        <v>184.162785306808</v>
+        <v>183.6097132585888</v>
       </c>
       <c r="O22" t="n">
-        <v>13.57065898572387</v>
+        <v>13.5502661692894</v>
       </c>
       <c r="P22" t="n">
-        <v>381.8262524313505</v>
+        <v>381.7619748271261</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32995,28 +33116,28 @@
         <v>0.0822</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7523264498209223</v>
+        <v>-0.742442628252886</v>
       </c>
       <c r="J23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K23" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1177871852971982</v>
+        <v>0.1156436900148302</v>
       </c>
       <c r="M23" t="n">
-        <v>12.23910576731333</v>
+        <v>12.23522228295986</v>
       </c>
       <c r="N23" t="n">
-        <v>211.8293814990151</v>
+        <v>211.5762521787381</v>
       </c>
       <c r="O23" t="n">
-        <v>14.55435953585781</v>
+        <v>14.54566093990707</v>
       </c>
       <c r="P23" t="n">
-        <v>382.1084472617301</v>
+        <v>381.9932755014766</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33073,28 +33194,28 @@
         <v>0.1105</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7153727570244798</v>
+        <v>-0.7058450846785901</v>
       </c>
       <c r="J24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K24" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1210054275886938</v>
+        <v>0.1187557551685587</v>
       </c>
       <c r="M24" t="n">
-        <v>11.3520673426646</v>
+        <v>11.34619919409767</v>
       </c>
       <c r="N24" t="n">
-        <v>185.7566438268489</v>
+        <v>185.5650574660272</v>
       </c>
       <c r="O24" t="n">
-        <v>13.62925690662733</v>
+        <v>13.6222265972207</v>
       </c>
       <c r="P24" t="n">
-        <v>387.7453890434709</v>
+        <v>387.6343673311058</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33151,28 +33272,28 @@
         <v>0.0989</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6930624438815445</v>
+        <v>-0.6836455310020513</v>
       </c>
       <c r="J25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K25" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1376215397948711</v>
+        <v>0.1349766098928191</v>
       </c>
       <c r="M25" t="n">
-        <v>10.06473300558072</v>
+        <v>10.0608914855315</v>
       </c>
       <c r="N25" t="n">
-        <v>150.4022861570734</v>
+        <v>150.3374141586588</v>
       </c>
       <c r="O25" t="n">
-        <v>12.26386098082791</v>
+        <v>12.26121585156459</v>
       </c>
       <c r="P25" t="n">
-        <v>396.174989593458</v>
+        <v>396.0652585117078</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -33229,28 +33350,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5682852143744465</v>
+        <v>-0.561024716098488</v>
       </c>
       <c r="J26" t="n">
+        <v>254</v>
+      </c>
+      <c r="K26" t="n">
         <v>253</v>
       </c>
-      <c r="K26" t="n">
-        <v>252</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.1140310916141631</v>
+        <v>0.1120517207390793</v>
       </c>
       <c r="M26" t="n">
-        <v>9.468686317793809</v>
+        <v>9.462059823089659</v>
       </c>
       <c r="N26" t="n">
-        <v>123.550221872448</v>
+        <v>123.3686265575026</v>
       </c>
       <c r="O26" t="n">
-        <v>11.11531474464165</v>
+        <v>11.10714304209244</v>
       </c>
       <c r="P26" t="n">
-        <v>394.3832665012108</v>
+        <v>394.2979154568122</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -33307,28 +33428,28 @@
         <v>0.0572</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5398717854935321</v>
+        <v>-0.5336121953115689</v>
       </c>
       <c r="J27" t="n">
+        <v>254</v>
+      </c>
+      <c r="K27" t="n">
         <v>253</v>
       </c>
-      <c r="K27" t="n">
-        <v>252</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.09873661821095769</v>
+        <v>0.09726867825209673</v>
       </c>
       <c r="M27" t="n">
-        <v>9.73086284489696</v>
+        <v>9.721710786776578</v>
       </c>
       <c r="N27" t="n">
-        <v>130.9997168288512</v>
+        <v>130.7099325824004</v>
       </c>
       <c r="O27" t="n">
-        <v>11.44551077186384</v>
+        <v>11.43284446594112</v>
       </c>
       <c r="P27" t="n">
-        <v>391.0091685057957</v>
+        <v>390.9355836719135</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -33385,28 +33506,28 @@
         <v>0.0688</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5313997955140818</v>
+        <v>-0.5276139773254224</v>
       </c>
       <c r="J28" t="n">
+        <v>254</v>
+      </c>
+      <c r="K28" t="n">
         <v>253</v>
       </c>
-      <c r="K28" t="n">
-        <v>252</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.09585416133363422</v>
+        <v>0.09529459781483451</v>
       </c>
       <c r="M28" t="n">
-        <v>9.991984979238657</v>
+        <v>9.970500082753153</v>
       </c>
       <c r="N28" t="n">
-        <v>131.1553161603572</v>
+        <v>130.7203154667755</v>
       </c>
       <c r="O28" t="n">
-        <v>11.4523061503069</v>
+        <v>11.4332985383386</v>
       </c>
       <c r="P28" t="n">
-        <v>382.2008408657356</v>
+        <v>382.1563365460562</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -33463,28 +33584,28 @@
         <v>0.0863</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7227717931221691</v>
+        <v>-0.7173138062622499</v>
       </c>
       <c r="J29" t="n">
+        <v>254</v>
+      </c>
+      <c r="K29" t="n">
         <v>253</v>
       </c>
-      <c r="K29" t="n">
-        <v>252</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.1939146502997277</v>
+        <v>0.192617092864144</v>
       </c>
       <c r="M29" t="n">
-        <v>8.710777862938658</v>
+        <v>8.703366807134872</v>
       </c>
       <c r="N29" t="n">
-        <v>106.9272541151356</v>
+        <v>106.6779613380361</v>
       </c>
       <c r="O29" t="n">
-        <v>10.34056352986314</v>
+        <v>10.3285023763388</v>
       </c>
       <c r="P29" t="n">
-        <v>378.7489765187423</v>
+        <v>378.6848149610775</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -33541,28 +33662,28 @@
         <v>0.0877</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7124978760961688</v>
+        <v>-0.704056875643476</v>
       </c>
       <c r="J30" t="n">
+        <v>254</v>
+      </c>
+      <c r="K30" t="n">
         <v>253</v>
       </c>
-      <c r="K30" t="n">
-        <v>252</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.2059356344826483</v>
+        <v>0.2027359480960936</v>
       </c>
       <c r="M30" t="n">
-        <v>8.387248352608413</v>
+        <v>8.394388399808442</v>
       </c>
       <c r="N30" t="n">
-        <v>96.38444917337821</v>
+        <v>96.41808666779775</v>
       </c>
       <c r="O30" t="n">
-        <v>9.817558208300994</v>
+        <v>9.819271188219508</v>
       </c>
       <c r="P30" t="n">
-        <v>380.8000996803903</v>
+        <v>380.7008712008805</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -33619,28 +33740,28 @@
         <v>0.1087</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6392502718396534</v>
+        <v>-0.6335525801937103</v>
       </c>
       <c r="J31" t="n">
+        <v>254</v>
+      </c>
+      <c r="K31" t="n">
         <v>253</v>
       </c>
-      <c r="K31" t="n">
-        <v>252</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.1788146705588411</v>
+        <v>0.1771333819670864</v>
       </c>
       <c r="M31" t="n">
-        <v>8.247129181072172</v>
+        <v>8.241469338781084</v>
       </c>
       <c r="N31" t="n">
-        <v>92.40500494471453</v>
+        <v>92.22867266383935</v>
       </c>
       <c r="O31" t="n">
-        <v>9.61275220447893</v>
+        <v>9.603576035198522</v>
       </c>
       <c r="P31" t="n">
-        <v>379.4503596705796</v>
+        <v>379.3833802548207</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -33697,28 +33818,28 @@
         <v>0.1004</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4192478287889204</v>
+        <v>-0.4175017701046612</v>
       </c>
       <c r="J32" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K32" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08502846583968948</v>
+        <v>0.08502513285288571</v>
       </c>
       <c r="M32" t="n">
-        <v>8.169196166253649</v>
+        <v>8.143117173380988</v>
       </c>
       <c r="N32" t="n">
-        <v>92.23438479871741</v>
+        <v>91.88588187646798</v>
       </c>
       <c r="O32" t="n">
-        <v>9.603873426837602</v>
+        <v>9.585712382315045</v>
       </c>
       <c r="P32" t="n">
-        <v>387.1902823186678</v>
+        <v>387.1696275132141</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -33775,28 +33896,28 @@
         <v>0.1039</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3747238633235545</v>
+        <v>-0.3757220988370037</v>
       </c>
       <c r="J33" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K33" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L33" t="n">
-        <v>0.08307288271596414</v>
+        <v>0.08412544490076712</v>
       </c>
       <c r="M33" t="n">
-        <v>7.129936349687314</v>
+        <v>7.106355191056507</v>
       </c>
       <c r="N33" t="n">
-        <v>75.57988187385568</v>
+        <v>75.28568371899742</v>
       </c>
       <c r="O33" t="n">
-        <v>8.693669068572582</v>
+        <v>8.676732318044474</v>
       </c>
       <c r="P33" t="n">
-        <v>396.3036255447708</v>
+        <v>396.3154340598643</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -33853,28 +33974,28 @@
         <v>0.0945</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5369924279410631</v>
+        <v>-0.5384012256450224</v>
       </c>
       <c r="J34" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K34" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1637012125973152</v>
+        <v>0.1655682270127696</v>
       </c>
       <c r="M34" t="n">
-        <v>6.981502451074172</v>
+        <v>6.959720903974837</v>
       </c>
       <c r="N34" t="n">
-        <v>71.83793926624959</v>
+        <v>71.56426480054436</v>
       </c>
       <c r="O34" t="n">
-        <v>8.475726474246889</v>
+        <v>8.45956646646531</v>
       </c>
       <c r="P34" t="n">
-        <v>384.3733003212124</v>
+        <v>384.3899655357101</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -33912,7 +34033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI254"/>
+  <dimension ref="A1:AI255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78741,6 +78862,183 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>-36.233526272840535,175.4772846852459</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>-36.23425054588581,175.47730827619137</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>-36.234975855831145,175.47725436010245</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-36.235700709882444,175.4772338037862</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-36.2364281548361,175.47718884461966</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-36.23715222623805,175.47727699945105</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-36.23786794982631,175.47743585715912</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-36.238588387426056,175.4775309144601</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-36.23930871195535,175.47762707627223</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-36.24002462672709,175.47775647288003</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-36.240738328934434,175.47788773954989</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>-36.24145328778621,175.47804041013706</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>-36.24216685482405,175.47820408409748</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>-36.24287370582054,175.47840145756408</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>-36.243593754953125,175.4785325102781</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>-36.24429199094643,175.47877308912723</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>-36.24497985451171,175.47906573235116</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>-36.245702099858576,175.4791856581279</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>-36.2463930688142,175.47946264044205</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>-36.24707582737073,175.4797601916842</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>-36.24774809515901,175.48004052339164</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>-36.24838258305919,175.48045714335458</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>-36.24900503240282,175.48091206678214</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>-36.249585109363366,175.48140781757405</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>-36.25016057769912,175.48191654189498</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>-36.25076488179391,175.482415184745</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>-36.25141163186692,175.48284495656122</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>-36.25203019546922,175.48331904910415</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>-36.25255812237144,175.48391716988647</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>-36.253061999660105,175.48455051136213</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>-36.25348723725512,175.48526689397224</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>-36.25381423753125,175.48596855764546</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>-36.25410574868296,175.48675882267636</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0120/nzd0120.xlsx
+++ b/data/nzd0120/nzd0120.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI255"/>
+  <dimension ref="A1:AI256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28733,6 +28733,117 @@
       <c r="AI255" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>363.77</v>
+      </c>
+      <c r="C256" t="n">
+        <v>365.47</v>
+      </c>
+      <c r="D256" t="n">
+        <v>364.51</v>
+      </c>
+      <c r="E256" t="n">
+        <v>356.27</v>
+      </c>
+      <c r="F256" t="n">
+        <v>353.78</v>
+      </c>
+      <c r="G256" t="n">
+        <v>356.79</v>
+      </c>
+      <c r="H256" t="n">
+        <v>365</v>
+      </c>
+      <c r="I256" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="J256" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="K256" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="L256" t="n">
+        <v>360.95</v>
+      </c>
+      <c r="M256" t="n">
+        <v>357.41</v>
+      </c>
+      <c r="N256" t="n">
+        <v>349.82</v>
+      </c>
+      <c r="O256" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="P256" t="n">
+        <v>342.91</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="R256" t="n">
+        <v>357.27</v>
+      </c>
+      <c r="S256" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="T256" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="U256" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="V256" t="n">
+        <v>366.81</v>
+      </c>
+      <c r="W256" t="n">
+        <v>369.1</v>
+      </c>
+      <c r="X256" t="n">
+        <v>377.19</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>384.16</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>387.04</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>386.56</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>374.93</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>366.17</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>378.39</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>369.68</v>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28747,7 +28858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B256"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31310,6 +31421,16 @@
       </c>
       <c r="B256" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -31478,28 +31599,28 @@
         <v>0.0663</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1418293499871855</v>
+        <v>-0.1400594885956202</v>
       </c>
       <c r="J2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003401417325195721</v>
+        <v>0.003345475189720948</v>
       </c>
       <c r="M2" t="n">
-        <v>14.53331540597689</v>
+        <v>14.48577447209936</v>
       </c>
       <c r="N2" t="n">
-        <v>294.4833675434112</v>
+        <v>293.314270851899</v>
       </c>
       <c r="O2" t="n">
-        <v>17.16051769450477</v>
+        <v>17.12642025794938</v>
       </c>
       <c r="P2" t="n">
-        <v>365.4450329161593</v>
+        <v>365.4241742712467</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31556,28 +31677,28 @@
         <v>0.0613</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.287467265709716</v>
+        <v>-0.2829136077523907</v>
       </c>
       <c r="J3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0141227234837582</v>
+        <v>0.01379382013162034</v>
       </c>
       <c r="M3" t="n">
-        <v>13.76121306886855</v>
+        <v>13.7330139623634</v>
       </c>
       <c r="N3" t="n">
-        <v>286.7760927131852</v>
+        <v>285.7644220432342</v>
       </c>
       <c r="O3" t="n">
-        <v>16.93446464206014</v>
+        <v>16.90456808212603</v>
       </c>
       <c r="P3" t="n">
-        <v>367.6280194843645</v>
+        <v>367.5743171749265</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31634,28 +31755,28 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3076095133457719</v>
+        <v>-0.3000610031499826</v>
       </c>
       <c r="J4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K4" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01591719427933569</v>
+        <v>0.01526794616539051</v>
       </c>
       <c r="M4" t="n">
-        <v>13.99293851166215</v>
+        <v>13.97638829796567</v>
       </c>
       <c r="N4" t="n">
-        <v>291.0226463095446</v>
+        <v>290.2000924722583</v>
       </c>
       <c r="O4" t="n">
-        <v>17.05938587140653</v>
+        <v>17.03526027016489</v>
       </c>
       <c r="P4" t="n">
-        <v>363.5921540865126</v>
+        <v>363.5032609904914</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31712,28 +31833,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2462667525018676</v>
+        <v>-0.243914291977455</v>
       </c>
       <c r="J5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K5" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01131634042289342</v>
+        <v>0.01119640064963723</v>
       </c>
       <c r="M5" t="n">
-        <v>13.01808064795532</v>
+        <v>12.97848982709051</v>
       </c>
       <c r="N5" t="n">
-        <v>263.7648330460019</v>
+        <v>262.754541524853</v>
       </c>
       <c r="O5" t="n">
-        <v>16.24083843420659</v>
+        <v>16.20970516464914</v>
       </c>
       <c r="P5" t="n">
-        <v>360.032362064669</v>
+        <v>360.0047048848618</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31790,28 +31911,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2960820635862356</v>
+        <v>-0.2973132026452829</v>
       </c>
       <c r="J6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02096129748550801</v>
+        <v>0.02130680781232863</v>
       </c>
       <c r="M6" t="n">
-        <v>11.46276248177556</v>
+        <v>11.42243194378086</v>
       </c>
       <c r="N6" t="n">
-        <v>205.5141265283101</v>
+        <v>204.7171978343985</v>
       </c>
       <c r="O6" t="n">
-        <v>14.33576389762018</v>
+        <v>14.30794177491642</v>
       </c>
       <c r="P6" t="n">
-        <v>363.2841806585791</v>
+        <v>363.298589565483</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31868,28 +31989,28 @@
         <v>0.0993</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3354993613560669</v>
+        <v>-0.3359863241499706</v>
       </c>
       <c r="J7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02420738468893502</v>
+        <v>0.02447673702609776</v>
       </c>
       <c r="M7" t="n">
-        <v>12.29131551411465</v>
+        <v>12.24516261212941</v>
       </c>
       <c r="N7" t="n">
-        <v>227.7345031353932</v>
+        <v>226.8428361252612</v>
       </c>
       <c r="O7" t="n">
-        <v>15.09087483002205</v>
+        <v>15.06130260386734</v>
       </c>
       <c r="P7" t="n">
-        <v>366.4342384563112</v>
+        <v>366.4399377325313</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31946,28 +32067,28 @@
         <v>0.0776</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4074238771772151</v>
+        <v>-0.4024871628055898</v>
       </c>
       <c r="J8" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K8" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03605598960068424</v>
+        <v>0.03548388742783581</v>
       </c>
       <c r="M8" t="n">
-        <v>12.05377702529386</v>
+        <v>12.02650131206661</v>
       </c>
       <c r="N8" t="n">
-        <v>222.7425190574113</v>
+        <v>222.0138765289902</v>
       </c>
       <c r="O8" t="n">
-        <v>14.92456093348851</v>
+        <v>14.90013008429759</v>
       </c>
       <c r="P8" t="n">
-        <v>369.8607377420799</v>
+        <v>369.8029598190507</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32024,28 +32145,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4690632376910308</v>
+        <v>-0.4697723000857806</v>
       </c>
       <c r="J9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05050730528656822</v>
+        <v>0.05105940806117515</v>
       </c>
       <c r="M9" t="n">
-        <v>11.74853814650247</v>
+        <v>11.70600781828267</v>
       </c>
       <c r="N9" t="n">
-        <v>207.6041382399914</v>
+        <v>206.7929927322131</v>
       </c>
       <c r="O9" t="n">
-        <v>14.40847452855407</v>
+        <v>14.38029877061715</v>
       </c>
       <c r="P9" t="n">
-        <v>377.8326395797109</v>
+        <v>377.8409382474852</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32102,28 +32223,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5727798214452455</v>
+        <v>-0.5810414391970471</v>
       </c>
       <c r="J10" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K10" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07373808900235668</v>
+        <v>0.07617309831974561</v>
       </c>
       <c r="M10" t="n">
-        <v>11.67980249904908</v>
+        <v>11.67658649271286</v>
       </c>
       <c r="N10" t="n">
-        <v>206.8488591038195</v>
+        <v>206.4433780555925</v>
       </c>
       <c r="O10" t="n">
-        <v>14.38224110157452</v>
+        <v>14.36813759871447</v>
       </c>
       <c r="P10" t="n">
-        <v>385.4626778053546</v>
+        <v>385.559369466777</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32180,28 +32301,28 @@
         <v>0.0703</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7615295058747209</v>
+        <v>-0.7674730686058104</v>
       </c>
       <c r="J11" t="n">
+        <v>255</v>
+      </c>
+      <c r="K11" t="n">
         <v>254</v>
       </c>
-      <c r="K11" t="n">
-        <v>253</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.09652469800352159</v>
+        <v>0.09856992760631622</v>
       </c>
       <c r="M11" t="n">
-        <v>12.85758488891431</v>
+        <v>12.83692597780955</v>
       </c>
       <c r="N11" t="n">
-        <v>273.4837621265236</v>
+        <v>272.6175640644926</v>
       </c>
       <c r="O11" t="n">
-        <v>16.53734447021418</v>
+        <v>16.51113454807066</v>
       </c>
       <c r="P11" t="n">
-        <v>392.3420473612261</v>
+        <v>392.4114826836586</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32258,28 +32379,28 @@
         <v>0.0771</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.920443026431026</v>
+        <v>-0.9279166442328879</v>
       </c>
       <c r="J12" t="n">
+        <v>255</v>
+      </c>
+      <c r="K12" t="n">
         <v>254</v>
       </c>
-      <c r="K12" t="n">
-        <v>253</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1376233503796517</v>
+        <v>0.1404220106595236</v>
       </c>
       <c r="M12" t="n">
-        <v>12.38481697161805</v>
+        <v>12.37234627674461</v>
       </c>
       <c r="N12" t="n">
-        <v>267.4723713237457</v>
+        <v>266.7521740092306</v>
       </c>
       <c r="O12" t="n">
-        <v>16.35458257870698</v>
+        <v>16.33254952569349</v>
       </c>
       <c r="P12" t="n">
-        <v>395.0033158511229</v>
+        <v>395.0906259520318</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32336,28 +32457,28 @@
         <v>0.0861</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7771780896755182</v>
+        <v>-0.7859405061614971</v>
       </c>
       <c r="J13" t="n">
+        <v>255</v>
+      </c>
+      <c r="K13" t="n">
         <v>254</v>
       </c>
-      <c r="K13" t="n">
-        <v>253</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1137205627897069</v>
+        <v>0.1166706925235418</v>
       </c>
       <c r="M13" t="n">
-        <v>12.36144751980176</v>
+        <v>12.3486371693342</v>
       </c>
       <c r="N13" t="n">
-        <v>237.1663184176259</v>
+        <v>236.6901296464685</v>
       </c>
       <c r="O13" t="n">
-        <v>15.40020514206307</v>
+        <v>15.38473690533798</v>
       </c>
       <c r="P13" t="n">
-        <v>389.1962901004949</v>
+        <v>389.2986565163164</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32414,28 +32535,28 @@
         <v>0.1244</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8620393242361816</v>
+        <v>-0.8729134540874537</v>
       </c>
       <c r="J14" t="n">
+        <v>255</v>
+      </c>
+      <c r="K14" t="n">
         <v>254</v>
       </c>
-      <c r="K14" t="n">
-        <v>253</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1371418177175455</v>
+        <v>0.140794682033344</v>
       </c>
       <c r="M14" t="n">
-        <v>12.50519737149972</v>
+        <v>12.51216057729719</v>
       </c>
       <c r="N14" t="n">
-        <v>235.5612868382823</v>
+        <v>235.3385203118063</v>
       </c>
       <c r="O14" t="n">
-        <v>15.3480059564193</v>
+        <v>15.34074705846512</v>
       </c>
       <c r="P14" t="n">
-        <v>386.5066613676128</v>
+        <v>386.6336977507651</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32492,28 +32613,28 @@
         <v>0.1041</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6983260709732733</v>
+        <v>-0.707203205347481</v>
       </c>
       <c r="J15" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K15" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1514410049452606</v>
+        <v>0.1553744236736605</v>
       </c>
       <c r="M15" t="n">
-        <v>9.956975605723835</v>
+        <v>9.955254707774589</v>
       </c>
       <c r="N15" t="n">
-        <v>137.1484341934461</v>
+        <v>137.078990536611</v>
       </c>
       <c r="O15" t="n">
-        <v>11.71103898864</v>
+        <v>11.70807373296782</v>
       </c>
       <c r="P15" t="n">
-        <v>380.1642187131309</v>
+        <v>380.2681142087951</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32570,28 +32691,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6189905872885523</v>
+        <v>-0.6324409612545266</v>
       </c>
       <c r="J16" t="n">
+        <v>255</v>
+      </c>
+      <c r="K16" t="n">
         <v>254</v>
       </c>
-      <c r="K16" t="n">
-        <v>253</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1266850682549046</v>
+        <v>0.1315592956731497</v>
       </c>
       <c r="M16" t="n">
-        <v>9.780728536596332</v>
+        <v>9.810192921810229</v>
       </c>
       <c r="N16" t="n">
-        <v>133.0741767334918</v>
+        <v>133.6283328801818</v>
       </c>
       <c r="O16" t="n">
-        <v>11.53577811564923</v>
+        <v>11.559772181154</v>
       </c>
       <c r="P16" t="n">
-        <v>376.2353717974158</v>
+        <v>376.3925050010885</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32648,28 +32769,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5771562534805412</v>
+        <v>-0.5859748196809227</v>
       </c>
       <c r="J17" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K17" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09342929478996975</v>
+        <v>0.09651632053416304</v>
       </c>
       <c r="M17" t="n">
-        <v>10.59257216778052</v>
+        <v>10.59225781558314</v>
       </c>
       <c r="N17" t="n">
-        <v>162.2337491027664</v>
+        <v>162.0597714654488</v>
       </c>
       <c r="O17" t="n">
-        <v>12.73710128336767</v>
+        <v>12.73026988973324</v>
       </c>
       <c r="P17" t="n">
-        <v>373.2242609771069</v>
+        <v>373.3274710072601</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32726,28 +32847,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5167631484480715</v>
+        <v>-0.5149279303150321</v>
       </c>
       <c r="J18" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K18" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07009817104505556</v>
+        <v>0.07017763889103767</v>
       </c>
       <c r="M18" t="n">
-        <v>11.07265474460265</v>
+        <v>11.03742789016242</v>
       </c>
       <c r="N18" t="n">
-        <v>177.8071697533706</v>
+        <v>177.1299056484051</v>
       </c>
       <c r="O18" t="n">
-        <v>13.33443548686522</v>
+        <v>13.30901595342064</v>
       </c>
       <c r="P18" t="n">
-        <v>368.9169939380784</v>
+        <v>368.8955150587975</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32804,28 +32925,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5547368651332248</v>
+        <v>-0.5586186692347932</v>
       </c>
       <c r="J19" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K19" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09971871655718589</v>
+        <v>0.1016882704737048</v>
       </c>
       <c r="M19" t="n">
-        <v>10.27442782782827</v>
+        <v>10.2533650999967</v>
       </c>
       <c r="N19" t="n">
-        <v>139.447707835767</v>
+        <v>138.9904178467938</v>
       </c>
       <c r="O19" t="n">
-        <v>11.80879789969186</v>
+        <v>11.78941974173427</v>
       </c>
       <c r="P19" t="n">
-        <v>370.2563749861734</v>
+        <v>370.3018065347118</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32882,28 +33003,28 @@
         <v>0.0849</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3295421564244401</v>
+        <v>-0.3339157904149387</v>
       </c>
       <c r="J20" t="n">
+        <v>255</v>
+      </c>
+      <c r="K20" t="n">
         <v>254</v>
       </c>
-      <c r="K20" t="n">
-        <v>253</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.03632419873842485</v>
+        <v>0.03753468429168028</v>
       </c>
       <c r="M20" t="n">
-        <v>10.11426765506725</v>
+        <v>10.09654383929167</v>
       </c>
       <c r="N20" t="n">
-        <v>145.1567083136429</v>
+        <v>144.6992142789724</v>
       </c>
       <c r="O20" t="n">
-        <v>12.04809978019949</v>
+        <v>12.02909864781948</v>
       </c>
       <c r="P20" t="n">
-        <v>369.7780187434789</v>
+        <v>369.8291134656299</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32960,28 +33081,28 @@
         <v>0.1177</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4637906778213911</v>
+        <v>-0.4634332397183189</v>
       </c>
       <c r="J21" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K21" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05421695450571695</v>
+        <v>0.05457190455937078</v>
       </c>
       <c r="M21" t="n">
-        <v>11.55535484654023</v>
+        <v>11.51172836857946</v>
       </c>
       <c r="N21" t="n">
-        <v>188.3372474349476</v>
+        <v>187.5994293874236</v>
       </c>
       <c r="O21" t="n">
-        <v>13.72360183898336</v>
+        <v>13.69669410432399</v>
       </c>
       <c r="P21" t="n">
-        <v>376.5505187919934</v>
+        <v>376.5463354364957</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33038,28 +33159,28 @@
         <v>0.07729999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6239738092754937</v>
+        <v>-0.6224546767580773</v>
       </c>
       <c r="J22" t="n">
+        <v>255</v>
+      </c>
+      <c r="K22" t="n">
         <v>254</v>
       </c>
-      <c r="K22" t="n">
-        <v>253</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.09508946235666904</v>
+        <v>0.09539501358391533</v>
       </c>
       <c r="M22" t="n">
-        <v>11.58451307581631</v>
+        <v>11.5459314342493</v>
       </c>
       <c r="N22" t="n">
-        <v>183.6097132585888</v>
+        <v>182.9003072005885</v>
       </c>
       <c r="O22" t="n">
-        <v>13.5502661692894</v>
+        <v>13.52406400460263</v>
       </c>
       <c r="P22" t="n">
-        <v>381.7619748271261</v>
+        <v>381.7440553364245</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33116,28 +33237,28 @@
         <v>0.0822</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.742442628252886</v>
+        <v>-0.7367066025429346</v>
       </c>
       <c r="J23" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K23" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1156436900148302</v>
+        <v>0.1148288134666835</v>
       </c>
       <c r="M23" t="n">
-        <v>12.23522228295986</v>
+        <v>12.21273809339074</v>
       </c>
       <c r="N23" t="n">
-        <v>211.5762521787381</v>
+        <v>210.9421046610801</v>
       </c>
       <c r="O23" t="n">
-        <v>14.54566093990707</v>
+        <v>14.52384606986318</v>
       </c>
       <c r="P23" t="n">
-        <v>381.9932755014766</v>
+        <v>381.9261426623017</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33194,28 +33315,28 @@
         <v>0.1105</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7058450846785901</v>
+        <v>-0.6989217417871063</v>
       </c>
       <c r="J24" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K24" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1187557551685587</v>
+        <v>0.1174219653132116</v>
       </c>
       <c r="M24" t="n">
-        <v>11.34619919409767</v>
+        <v>11.3294810396237</v>
       </c>
       <c r="N24" t="n">
-        <v>185.5650574660272</v>
+        <v>185.1222542165775</v>
       </c>
       <c r="O24" t="n">
-        <v>13.6222265972207</v>
+        <v>13.60596392089063</v>
       </c>
       <c r="P24" t="n">
-        <v>387.6343673311058</v>
+        <v>387.5533384640138</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33272,28 +33393,28 @@
         <v>0.0989</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6836455310020513</v>
+        <v>-0.6783869791940367</v>
       </c>
       <c r="J25" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K25" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1349766098928191</v>
+        <v>0.1340344287616735</v>
       </c>
       <c r="M25" t="n">
-        <v>10.0608914855315</v>
+        <v>10.04110642525792</v>
       </c>
       <c r="N25" t="n">
-        <v>150.3374141586588</v>
+        <v>149.9122161656161</v>
       </c>
       <c r="O25" t="n">
-        <v>12.26121585156459</v>
+        <v>12.24386442940366</v>
       </c>
       <c r="P25" t="n">
-        <v>396.0652585117078</v>
+        <v>396.0037138934179</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -33350,28 +33471,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.561024716098488</v>
+        <v>-0.5546029274712533</v>
       </c>
       <c r="J26" t="n">
+        <v>255</v>
+      </c>
+      <c r="K26" t="n">
         <v>254</v>
       </c>
-      <c r="K26" t="n">
-        <v>253</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.1120517207390793</v>
+        <v>0.1104234707667716</v>
       </c>
       <c r="M26" t="n">
-        <v>9.462059823089659</v>
+        <v>9.451634719075804</v>
       </c>
       <c r="N26" t="n">
-        <v>123.3686265575026</v>
+        <v>123.1228153630926</v>
       </c>
       <c r="O26" t="n">
-        <v>11.10714304209244</v>
+        <v>11.09607206911944</v>
       </c>
       <c r="P26" t="n">
-        <v>394.2979154568122</v>
+        <v>394.2220962817694</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -33428,28 +33549,28 @@
         <v>0.0572</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5336121953115689</v>
+        <v>-0.5254322173099646</v>
       </c>
       <c r="J27" t="n">
+        <v>255</v>
+      </c>
+      <c r="K27" t="n">
         <v>254</v>
       </c>
-      <c r="K27" t="n">
-        <v>253</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.09726867825209673</v>
+        <v>0.09506313916362674</v>
       </c>
       <c r="M27" t="n">
-        <v>9.721710786776578</v>
+        <v>9.72116023326751</v>
       </c>
       <c r="N27" t="n">
-        <v>130.7099325824004</v>
+        <v>130.5845581844353</v>
       </c>
       <c r="O27" t="n">
-        <v>11.43284446594112</v>
+        <v>11.42736007065654</v>
       </c>
       <c r="P27" t="n">
-        <v>390.9355836719135</v>
+        <v>390.8390063443259</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -33506,28 +33627,28 @@
         <v>0.0688</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5276139773254224</v>
+        <v>-0.5218995450049045</v>
       </c>
       <c r="J28" t="n">
+        <v>255</v>
+      </c>
+      <c r="K28" t="n">
         <v>254</v>
       </c>
-      <c r="K28" t="n">
-        <v>253</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.09529459781483451</v>
+        <v>0.09403206014674204</v>
       </c>
       <c r="M28" t="n">
-        <v>9.970500082753153</v>
+        <v>9.958483462975444</v>
       </c>
       <c r="N28" t="n">
-        <v>130.7203154667755</v>
+        <v>130.3956232569252</v>
       </c>
       <c r="O28" t="n">
-        <v>11.4332985383386</v>
+        <v>11.41909029900916</v>
       </c>
       <c r="P28" t="n">
-        <v>382.1563365460562</v>
+        <v>382.0888688093352</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -33584,28 +33705,28 @@
         <v>0.0863</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7173138062622499</v>
+        <v>-0.7117488915297784</v>
       </c>
       <c r="J29" t="n">
+        <v>255</v>
+      </c>
+      <c r="K29" t="n">
         <v>254</v>
       </c>
-      <c r="K29" t="n">
-        <v>253</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.192617092864144</v>
+        <v>0.1912576854027447</v>
       </c>
       <c r="M29" t="n">
-        <v>8.703366807134872</v>
+        <v>8.696825683326288</v>
       </c>
       <c r="N29" t="n">
-        <v>106.6779613380361</v>
+        <v>106.4381138150835</v>
       </c>
       <c r="O29" t="n">
-        <v>10.3285023763388</v>
+        <v>10.31688488910696</v>
       </c>
       <c r="P29" t="n">
-        <v>378.6848149610775</v>
+        <v>378.6191125113876</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -33662,28 +33783,28 @@
         <v>0.0877</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.704056875643476</v>
+        <v>-0.6950553143681143</v>
       </c>
       <c r="J30" t="n">
+        <v>255</v>
+      </c>
+      <c r="K30" t="n">
         <v>254</v>
       </c>
-      <c r="K30" t="n">
-        <v>253</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.2027359480960936</v>
+        <v>0.1991831779112891</v>
       </c>
       <c r="M30" t="n">
-        <v>8.394388399808442</v>
+        <v>8.404193949395886</v>
       </c>
       <c r="N30" t="n">
-        <v>96.41808666779775</v>
+        <v>96.50983359582527</v>
       </c>
       <c r="O30" t="n">
-        <v>9.819271188219508</v>
+        <v>9.823941856292986</v>
       </c>
       <c r="P30" t="n">
-        <v>380.7008712008805</v>
+        <v>380.5945938084572</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -33740,28 +33861,28 @@
         <v>0.1087</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6335525801937103</v>
+        <v>-0.6268418044131655</v>
       </c>
       <c r="J31" t="n">
+        <v>255</v>
+      </c>
+      <c r="K31" t="n">
         <v>254</v>
       </c>
-      <c r="K31" t="n">
-        <v>253</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.1771333819670864</v>
+        <v>0.1748652869533684</v>
       </c>
       <c r="M31" t="n">
-        <v>8.241469338781084</v>
+        <v>8.240258241483803</v>
       </c>
       <c r="N31" t="n">
-        <v>92.22867266383935</v>
+        <v>92.12753630027373</v>
       </c>
       <c r="O31" t="n">
-        <v>9.603576035198522</v>
+        <v>9.598309033380501</v>
       </c>
       <c r="P31" t="n">
-        <v>379.3833802548207</v>
+        <v>379.3041491382092</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -33818,28 +33939,28 @@
         <v>0.1004</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4175017701046612</v>
+        <v>-0.4154637726632991</v>
       </c>
       <c r="J32" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K32" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08502513285288571</v>
+        <v>0.08490767263717525</v>
       </c>
       <c r="M32" t="n">
-        <v>8.143117173380988</v>
+        <v>8.118198801440572</v>
       </c>
       <c r="N32" t="n">
-        <v>91.88588187646798</v>
+        <v>91.54653817835204</v>
       </c>
       <c r="O32" t="n">
-        <v>9.585712382315045</v>
+        <v>9.567995515172028</v>
       </c>
       <c r="P32" t="n">
-        <v>387.1696275132141</v>
+        <v>387.1454152440164</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -33896,28 +34017,28 @@
         <v>0.1039</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3757220988370037</v>
+        <v>-0.3762196104383352</v>
       </c>
       <c r="J33" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K33" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L33" t="n">
-        <v>0.08412544490076712</v>
+        <v>0.08498961519734638</v>
       </c>
       <c r="M33" t="n">
-        <v>7.106355191056507</v>
+        <v>7.080582803195184</v>
       </c>
       <c r="N33" t="n">
-        <v>75.28568371899742</v>
+        <v>74.9895326521829</v>
       </c>
       <c r="O33" t="n">
-        <v>8.676732318044474</v>
+        <v>8.659649684149059</v>
       </c>
       <c r="P33" t="n">
-        <v>396.3154340598643</v>
+        <v>396.3213447075304</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -33974,28 +34095,28 @@
         <v>0.0945</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5384012256450224</v>
+        <v>-0.5385704353028048</v>
       </c>
       <c r="J34" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K34" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1655682270127696</v>
+        <v>0.1668379649133881</v>
       </c>
       <c r="M34" t="n">
-        <v>6.959720903974837</v>
+        <v>6.932912645199148</v>
       </c>
       <c r="N34" t="n">
-        <v>71.56426480054436</v>
+        <v>71.28156644716026</v>
       </c>
       <c r="O34" t="n">
-        <v>8.45956646646531</v>
+        <v>8.442841135966036</v>
       </c>
       <c r="P34" t="n">
-        <v>384.3899655357101</v>
+        <v>384.3919758178145</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -34033,7 +34154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI255"/>
+  <dimension ref="A1:AI256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79039,6 +79160,183 @@
         </is>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>-36.233525700882694,175.4773271634473</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>-36.23425003679632,175.477346084363</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>-36.23497476428302,175.47733542602114</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-36.23570057512535,175.47724381201718</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>-36.236427237615764,175.4772159584167</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-36.23715092584944,175.47729427535478</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-36.23786405495013,175.47747627911556</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-36.23858556734368,175.47756018198817</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-36.23931115958857,175.47760167403558</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-36.24002611840994,175.47774426510756</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>-36.2407445017855,175.47785217617107</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>-36.2414585565956,175.478013947347</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>-36.2421811774438,175.47813214787834</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>-36.24288632959556,175.47833805378175</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>-36.24360861536149,175.47845787245197</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>-36.244306636420184,175.4786995308351</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>-36.24499028495523,175.47901334460607</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>-36.24571111093302,175.47914039903304</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>-36.24640663931783,175.47939448120306</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>-36.24709230296045,175.47969127339297</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>-36.24776511699896,175.47999119814958</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>-36.24840322264754,175.4804072058586</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>-36.24901833957714,175.48088124342095</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>-36.24961006133208,175.48136070974127</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>-36.25016581572033,175.48190804379274</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>-36.25075184124509,175.48243634157478</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>-36.251398700399754,175.48286593646972</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>-36.25202936016676,175.48332036085972</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>-36.25255345558531,175.48392320388422</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>-36.25305346060235,175.48455991583933</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>-36.2534848937303,175.48526915323967</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>-36.25380966302423,175.48597091030595</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>-36.254093206857604,175.48676194488328</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
